--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1570,6 +1570,130 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122222705</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ettingsand, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>623034</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6681879</v>
+      </c>
+      <c r="S9" t="n">
+        <v>27</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Wahlgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Wahlgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -1575,7 +1575,7 @@
         <v>122222705</v>
       </c>
       <c r="B9" t="n">
-        <v>57315</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -1590,11 +1590,6 @@
       <c r="E9" t="n">
         <v>102622</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Pärluggla</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Aegolius funereus</t>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -1575,7 +1575,7 @@
         <v>122222705</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>57324</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1589,6 +1589,11 @@
       </c>
       <c r="E9" t="n">
         <v>102622</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -1575,12 +1575,7 @@
         <v>122222705</v>
       </c>
       <c r="B9" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -1575,7 +1575,7 @@
         <v>122222705</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57718</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -1575,7 +1575,7 @@
         <v>122222705</v>
       </c>
       <c r="B9" t="n">
-        <v>57718</v>
+        <v>57719</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -1575,7 +1575,7 @@
         <v>122222705</v>
       </c>
       <c r="B9" t="n">
-        <v>57719</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -1575,7 +1575,7 @@
         <v>122222705</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -1575,7 +1575,7 @@
         <v>122222705</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98531398</v>
+        <v>111490387</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ettingsandsinfarten, Upl</t>
+          <t>Jugansbovallen, 2,3 km V-ut, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623032.3596891968</v>
+        <v>623095</v>
       </c>
       <c r="R2" t="n">
-        <v>6681881.86329368</v>
+        <v>6682008</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:22</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:22</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,37 +758,47 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Trädlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kalle Brinell</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kalle Brinell</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>98753229</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -851,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623032.3596891968</v>
+        <v>623032</v>
       </c>
       <c r="R3" t="n">
-        <v>6681881.86329368</v>
+        <v>6681881</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -923,32 +910,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101266977</v>
+        <v>98753212</v>
       </c>
       <c r="B4" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -975,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623032.3596891968</v>
+        <v>623032</v>
       </c>
       <c r="R4" t="n">
-        <v>6681881.86329368</v>
+        <v>6681881</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1005,22 +987,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>03:38</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>03:38</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,69 +1029,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111491055</v>
+        <v>82675044</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57785</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102622</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jugansbovallen, 2,4 km V-ut, Upl</t>
+          <t>Östra Toften 222,Heby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622949.6897910746</v>
+        <v>623028</v>
       </c>
       <c r="R5" t="n">
-        <v>6682105.588167573</v>
+        <v>6681879</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,27 +1106,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2020-03-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2020-03-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett blommande exemplar.</t>
+          <t>00:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,80 +1130,78 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Teodor Carselind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Teodor Carselind, Henry Leinonen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111490387</v>
+        <v>122222705</v>
       </c>
       <c r="B6" t="n">
-        <v>93289</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>102622</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jugansbovallen, 2,3 km V-ut, Upl</t>
+          <t>Ettingsand, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623094.7587502389</v>
+        <v>623034</v>
       </c>
       <c r="R6" t="n">
-        <v>6682008.649094778</v>
+        <v>6681879</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,22 +1225,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,97 +1249,78 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Trädlåga</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Erik Wahlgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Erik Wahlgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111491056</v>
+        <v>101266977</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jugansbovallen, 2,4 km V-ut, Upl</t>
+          <t>Ettingsandsinfarten, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622970.0202536918</v>
+        <v>623032</v>
       </c>
       <c r="R7" t="n">
-        <v>6682092.861666769</v>
+        <v>6681881</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1397,22 +1344,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2022-05-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2022-05-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,87 +1368,78 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111491057</v>
+        <v>98531426</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jugansbovallen, 2,4 km V-ut, Upl</t>
+          <t>Ettingsandsinfarten, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622999.8269515566</v>
+        <v>623032</v>
       </c>
       <c r="R8" t="n">
-        <v>6682079.461113866</v>
+        <v>6681881</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1525,22 +1463,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,83 +1487,78 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122222705</v>
+        <v>98531398</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102622</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ettingsand, Upl</t>
+          <t>Ettingsandsinfarten, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623034</v>
+        <v>623032</v>
       </c>
       <c r="R9" t="n">
-        <v>6681879</v>
+        <v>6681881</v>
       </c>
       <c r="S9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1649,22 +1582,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,15 +1612,1030 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Wahlgren</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Wahlgren</t>
+          <t>Kalle Brinell</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>98531492</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ettingsandsinfarten, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>623032</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6681881</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-02-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-02-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111491053</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jugansbovallen, 2,4 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>622976</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6682134</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111491054</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jugansbovallen, 2,4 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>622983</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6682147</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111491055</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jugansbovallen, 2,4 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>622950</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6682106</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ett blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111491056</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jugansbovallen, 2,4 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>622970</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6682093</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>111491057</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jugansbovallen, 2,4 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>623000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6682079</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>111491060</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jugansbovallen, 2,3 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>623103</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6682030</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>111491061</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jugansbovallen, 2,3 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>623103</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6682030</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>111491059</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jugansbovallen, 2,3 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>623103</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6682008</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54808-2024 artfynd.xlsx
+++ b/artfynd/A 54808-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490387</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98753229</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98753212</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82675044</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122222705</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,6 +1413,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101266977</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1502,6 +1537,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98531426</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98531398</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1740,6 +1785,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98531492</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1853,6 +1903,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491053</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1966,6 +2021,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491054</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2089,6 +2149,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491055</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2202,6 +2267,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491056</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2315,6 +2385,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491057</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2428,6 +2503,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491060</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2532,6 +2612,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491061</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2636,8 +2721,32 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491059</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>